--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_403_R45.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_403_R45.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4277</v>
+        <v>5.3067</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5615</v>
+        <v>3.588</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8662</v>
+        <v>1.7187</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2148</v>
+        <v>0.8102</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2603</v>
+        <v>0.4152</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4751</v>
+        <v>0.395</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2065</v>
+        <v>0.3956</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0746</v>
+        <v>-0.0555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2811</v>
+        <v>0.4511</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0083</v>
+        <v>0.4146</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1857</v>
+        <v>0.4707</v>
       </c>
       <c r="O2" t="n">
-        <v>0.194</v>
+        <v>-0.0561</v>
       </c>
       <c r="P2" t="n">
+        <v>1.8198</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-0.2275</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-2.7297</v>
-      </c>
       <c r="R2" t="n">
-        <v>2.5022</v>
+        <v>2.0473</v>
       </c>
       <c r="S2" t="n">
-        <v>1.08</v>
+        <v>0.3382</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7243</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6443</v>
+        <v>0.347</v>
       </c>
       <c r="V2" t="n">
-        <v>4.3604</v>
+        <v>2.3386</v>
       </c>
       <c r="W2" t="n">
-        <v>4.3604</v>
+        <v>3.4287</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8129</v>
+        <v>5.2068</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0942</v>
+        <v>3.0497</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7187</v>
+        <v>2.1571</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8102</v>
+        <v>0.2148</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4152</v>
+        <v>-0.2603</v>
       </c>
       <c r="I3" t="n">
-        <v>0.395</v>
+        <v>0.4751</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3956</v>
+        <v>0.2065</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0555</v>
+        <v>-0.0746</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4511</v>
+        <v>0.2811</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4146</v>
+        <v>0.0083</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4707</v>
+        <v>-0.1857</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0561</v>
+        <v>0.194</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8198</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2275</v>
+        <v>-2.7297</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0473</v>
+        <v>2.5022</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1556</v>
+        <v>0.859</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5026</v>
+        <v>1.2124</v>
       </c>
       <c r="U3" t="n">
-        <v>0.347</v>
+        <v>-0.3534</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3386</v>
+        <v>4.3604</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4287</v>
+        <v>4.3604</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9791</v>
+        <v>4.0456</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9121</v>
+        <v>2.5672</v>
       </c>
       <c r="F4" t="n">
-        <v>4.8913</v>
+        <v>1.4784</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0094</v>
+        <v>2.5996</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5167</v>
+        <v>1.3836</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4927</v>
+        <v>1.2161</v>
       </c>
       <c r="J4" t="n">
-        <v>1.099</v>
+        <v>2.3064</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2341</v>
+        <v>0.8454</v>
       </c>
       <c r="L4" t="n">
-        <v>0.865</v>
+        <v>1.461</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9104</v>
+        <v>0.2933</v>
       </c>
       <c r="N4" t="n">
-        <v>1.2827</v>
+        <v>0.5382</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6277</v>
+        <v>-0.2449</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4549</v>
+        <v>0.6824</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5022</v>
+        <v>-0.2275</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0473</v>
+        <v>0.9099</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4247</v>
+        <v>0.2185</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4911</v>
+        <v>-0.0568</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9336</v>
+        <v>0.2752</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6307</v>
+        <v>4.0061</v>
       </c>
       <c r="E5" t="n">
-        <v>2.217</v>
+        <v>-0.8852</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4138</v>
+        <v>4.8913</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5996</v>
+        <v>3.0094</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3836</v>
+        <v>1.5167</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2161</v>
+        <v>1.4927</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3064</v>
+        <v>1.099</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8454</v>
+        <v>0.2341</v>
       </c>
       <c r="L5" t="n">
-        <v>1.461</v>
+        <v>0.865</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2933</v>
+        <v>1.9104</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5382</v>
+        <v>1.2827</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2449</v>
+        <v>0.6277</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6824</v>
+        <v>-0.4549</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2275</v>
+        <v>-2.5022</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9099</v>
+        <v>2.0473</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1964</v>
+        <v>1.4516</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.407</v>
+        <v>0.518</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2106</v>
+        <v>0.9336</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1505</v>
+        <v>2.0796</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4918</v>
+        <v>2.4196</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6423</v>
+        <v>-0.34</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9925</v>
+        <v>1.5371</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0701</v>
+        <v>1.3457</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9224</v>
+        <v>0.1914</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1267</v>
+        <v>1.3557</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1399</v>
+        <v>1.1694</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2666</v>
+        <v>0.1863</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8658</v>
+        <v>0.1814</v>
       </c>
       <c r="N6" t="n">
-        <v>0.21</v>
+        <v>0.1763</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6558</v>
+        <v>0.0051</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3648</v>
+        <v>-1.5923</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3648</v>
+        <v>1.5923</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7049</v>
+        <v>0.3142</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2932</v>
+        <v>0.476</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4117</v>
+        <v>-0.1618</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5468</v>
+        <v>0.2284</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.5468</v>
+        <v>2.1802</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.9519</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9736</v>
+        <v>1.619</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7641</v>
+        <v>-0.9587</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2095</v>
+        <v>2.5777</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5371</v>
+        <v>1.9925</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3457</v>
+        <v>0.0701</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1914</v>
+        <v>1.9224</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3557</v>
+        <v>1.1267</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1694</v>
+        <v>-0.1399</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1863</v>
+        <v>1.2666</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1814</v>
+        <v>0.8658</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1763</v>
+        <v>0.21</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0051</v>
+        <v>0.6558</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.5923</v>
+        <v>-1.3648</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5923</v>
+        <v>1.3648</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2082</v>
+        <v>1.1733</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1795</v>
+        <v>0.8262</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3876</v>
+        <v>0.3471</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2284</v>
+        <v>-1.5468</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1802</v>
+        <v>-1.5468</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.9519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3618</v>
+        <v>-0.4502</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3928</v>
+        <v>-3.4078</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0311</v>
+        <v>2.9576</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1686</v>
+        <v>-1.3679</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8465</v>
+        <v>-0.7254</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.0151</v>
+        <v>-0.6425</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.3275</v>
+        <v>-2.5956</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6365</v>
+        <v>-1.453</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.9639</v>
+        <v>-1.1426</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8411999999999999</v>
+        <v>1.2277</v>
       </c>
       <c r="N8" t="n">
-        <v>0.21</v>
+        <v>0.7276</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0512</v>
+        <v>0.5001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1374</v>
+        <v>0.9099</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2275</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3648</v>
+        <v>0.9099</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5794</v>
+        <v>0.7812</v>
       </c>
       <c r="T8" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.0388</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5075</v>
+        <v>0.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0901</v>
+        <v>-0.7734</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0901</v>
+        <v>-0.7734</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4843</v>
+        <v>-0.8215</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6681</v>
+        <v>-1.6263</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1838</v>
+        <v>0.8048</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3679</v>
+        <v>-3.1686</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7254</v>
+        <v>0.8465</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6425</v>
+        <v>-4.0151</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5956</v>
+        <v>-2.3275</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.453</v>
+        <v>0.6365</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1426</v>
+        <v>-2.9639</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2277</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7276</v>
+        <v>0.21</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5001</v>
+        <v>-1.0512</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9099</v>
+        <v>1.1374</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.2275</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9099</v>
+        <v>1.3648</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7471</v>
+        <v>0.1197</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2992</v>
+        <v>-0.1615</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0462</v>
+        <v>0.2812</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7734</v>
+        <v>1.0901</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7734</v>
+        <v>1.0901</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2222</v>
+        <v>-0.9165</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9046</v>
+        <v>-1.6827</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3176</v>
+        <v>0.7662</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.306</v>
+        <v>-1.2756</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9335</v>
+        <v>0.2104</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3725</v>
+        <v>-1.486</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.761</v>
+        <v>-0.8508</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.761</v>
+        <v>-0.4159</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.4348</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5451</v>
+        <v>-0.4249</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1725</v>
+        <v>0.6263</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3725</v>
+        <v>-1.0512</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2275</v>
+        <v>0.9099</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.2275</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2275</v>
+        <v>1.1374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1437</v>
+        <v>-0.5507</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1437</v>
+        <v>-0.6045</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.0537</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3748</v>
+        <v>-1.1055</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9553</v>
+        <v>-0.7879</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5805</v>
+        <v>-0.3176</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0699</v>
+        <v>-1.306</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9691</v>
+        <v>-0.9335</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.039</v>
+        <v>-0.3725</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2595</v>
+        <v>-0.761</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5866</v>
+        <v>-0.761</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3271</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3293</v>
+        <v>-0.5451</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3825</v>
+        <v>-0.1725</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7119</v>
+        <v>-0.3725</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5923</v>
+        <v>0.2275</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2747</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6824</v>
+        <v>0.2275</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2874</v>
+        <v>-0.0269</v>
       </c>
       <c r="T11" t="n">
-        <v>0.06</v>
+        <v>-0.0269</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2274</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7712</v>
+        <v>-1.4916</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.988</v>
+        <v>-2.2337</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2167</v>
+        <v>0.7421</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2756</v>
+        <v>-0.0699</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2104</v>
+        <v>0.9691</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.486</v>
+        <v>-1.039</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8508</v>
+        <v>0.2595</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4159</v>
+        <v>0.5866</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4348</v>
+        <v>-0.3271</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4249</v>
+        <v>-0.3293</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6263</v>
+        <v>0.3825</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0512</v>
+        <v>-0.7119</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9099</v>
+        <v>-1.5923</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2275</v>
+        <v>-2.2747</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1374</v>
+        <v>0.6824</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4055</v>
+        <v>0.1706</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9098000000000001</v>
+        <v>-0.2184</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4957</v>
+        <v>0.389</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.7602</v>
+        <v>17.4785</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6759000000000011</v>
+        <v>0.04220000000000113</v>
       </c>
       <c r="F13" t="n">
         <v>17.4363</v>
       </c>
       <c r="G13" t="n">
-        <v>2.975600000000001</v>
+        <v>2.9756</v>
       </c>
       <c r="H13" t="n">
         <v>4.838099999999999</v>
@@ -1444,7 +1444,7 @@
         <v>0.2145000000000006</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5721000000000002</v>
       </c>
       <c r="L13" t="n">
         <v>-0.3573000000000006</v>
@@ -1468,10 +1468,10 @@
         <v>14.7858</v>
       </c>
       <c r="S13" t="n">
-        <v>4.130500000000001</v>
+        <v>4.8487</v>
       </c>
       <c r="T13" t="n">
-        <v>1.198799999999999</v>
+        <v>1.9169</v>
       </c>
       <c r="U13" t="n">
         <v>2.9316</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4235</v>
+        <v>7.0255</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1233</v>
+        <v>5.2906</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3002</v>
+        <v>1.7349</v>
       </c>
       <c r="G14" t="n">
         <v>6.0399</v>
@@ -1546,13 +1546,13 @@
         <v>1.5923</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2787</v>
+        <v>0.3233</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2809</v>
+        <v>-0.1135</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0022</v>
+        <v>0.4368</v>
       </c>
       <c r="V14" t="n">
         <v>-0.475</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.325</v>
+        <v>0.5876</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8325</v>
+        <v>0.3655</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4925</v>
+        <v>0.222</v>
       </c>
       <c r="G15" t="n">
         <v>0.3242</v>
@@ -1624,13 +1624,13 @@
         <v>0.9099</v>
       </c>
       <c r="S15" t="n">
-        <v>0.09089999999999999</v>
+        <v>-0.6465</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2273</v>
+        <v>-0.6943</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3183</v>
+        <v>0.0478</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.887</v>
+        <v>0.3997</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4464</v>
+        <v>-0.4875</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4406</v>
+        <v>0.8872</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5943</v>
@@ -1702,13 +1702,13 @@
         <v>0.6824</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9363</v>
+        <v>0.449</v>
       </c>
       <c r="T16" t="n">
-        <v>0.91</v>
+        <v>-0.0238</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0263</v>
+        <v>0.4728</v>
       </c>
       <c r="V16" t="n">
         <v>1.0901</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2952</v>
+        <v>0.1556</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5324</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8277</v>
+        <v>0.1556</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4917</v>
+        <v>0.3113</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0007</v>
+        <v>0.1556</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4909</v>
+        <v>0.1556</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0359</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0345</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5276</v>
+        <v>0.3113</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0338</v>
+        <v>0.1556</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5614</v>
+        <v>0.1556</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9099</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2275</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7134</v>
+        <v>-0.1556</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3591</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0726</v>
+        <v>-0.1556</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1556</v>
+        <v>0.0307</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-1.5324</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1556</v>
+        <v>1.5631</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3113</v>
+        <v>0.4917</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1556</v>
+        <v>0.0007</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1556</v>
+        <v>0.4909</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.0359</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3113</v>
+        <v>0.5276</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1556</v>
+        <v>-0.0338</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1556</v>
+        <v>0.5614</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.2275</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1556</v>
+        <v>0.4489</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.3591</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1556</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7978</v>
+        <v>-0.9852</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0549</v>
+        <v>-2.1716</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2571</v>
+        <v>1.1865</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2519</v>
@@ -1936,13 +1936,13 @@
         <v>0.9099</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5914</v>
+        <v>0.4041</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1318</v>
+        <v>0.0151</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4596</v>
+        <v>0.389</v>
       </c>
       <c r="V19" t="n">
         <v>1.0901</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8169</v>
+        <v>-1.064</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1657</v>
+        <v>-2.8868</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3488</v>
+        <v>1.8228</v>
       </c>
       <c r="G20" t="n">
-        <v>0.014</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6218</v>
+        <v>-0.0011</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6359</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6692</v>
+        <v>-0.0017</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7437</v>
+        <v>0.2014</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0745</v>
+        <v>-0.2032</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6832</v>
+        <v>-0.6924</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1219</v>
+        <v>-0.2026</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5614</v>
+        <v>-0.4899</v>
       </c>
       <c r="P20" t="n">
         <v>-0.9099</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1374</v>
+        <v>-2.7297</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2275</v>
+        <v>1.8198</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0789</v>
+        <v>-0.2334</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3591</v>
+        <v>-0.1554</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4381</v>
+        <v>-0.078</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.7734</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.7734</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.157</v>
+        <v>-1.0755</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0593</v>
+        <v>-2.1657</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9022</v>
+        <v>1.0902</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8458</v>
+        <v>0.014</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0014</v>
+        <v>-0.6218</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1556</v>
+        <v>0.6359</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5565</v>
+        <v>-0.6692</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7782</v>
+        <v>-0.7437</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7782</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7107</v>
+        <v>0.6832</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2232</v>
+        <v>0.1219</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9339</v>
+        <v>0.5614</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4549</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4549</v>
+        <v>0.2275</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7662</v>
+        <v>-0.1796</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5028</v>
+        <v>-0.3591</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2635</v>
+        <v>0.1795</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3548</v>
+        <v>-1.157</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5851</v>
+        <v>-2.0593</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9399</v>
+        <v>0.9022</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4169</v>
+        <v>-0.8458</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6083</v>
+        <v>-1.0014</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1914</v>
+        <v>0.1556</v>
       </c>
       <c r="J22" t="n">
-        <v>0.058</v>
+        <v>-1.5565</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1282</v>
+        <v>-0.7782</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1863</v>
+        <v>-0.7782</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.475</v>
+        <v>0.7107</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4801</v>
+        <v>-0.2232</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0051</v>
+        <v>0.9339</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9099</v>
+        <v>0.4549</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4549</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3648</v>
+        <v>0.4549</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6491</v>
+        <v>-0.7662</v>
       </c>
       <c r="T22" t="n">
-        <v>0.982</v>
+        <v>-0.5028</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3329</v>
+        <v>-0.2635</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4969</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9894</v>
+        <v>-1.4082</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8868</v>
+        <v>-0.2321</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8974</v>
+        <v>-1.1761</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.4169</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0011</v>
+        <v>-0.6083</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6929999999999999</v>
+        <v>0.1914</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0017</v>
+        <v>0.058</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2014</v>
+        <v>-0.1282</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2032</v>
+        <v>0.1863</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6924</v>
+        <v>-0.475</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2026</v>
+        <v>-0.4801</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4899</v>
+        <v>0.0051</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9099</v>
+        <v>0.9099</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7297</v>
+        <v>-0.4549</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8198</v>
+        <v>1.3648</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1588</v>
+        <v>0.5957</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1554</v>
+        <v>0.1649</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0034</v>
+        <v>0.4309</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7734</v>
+        <v>-2.4969</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.7734</v>
+        <v>-2.4969</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2414</v>
+        <v>-4.4111</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1494</v>
+        <v>-1.5657</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.092</v>
+        <v>-2.8454</v>
       </c>
       <c r="G24" t="n">
         <v>-1.239</v>
@@ -2326,13 +2326,13 @@
         <v>1.3648</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1862</v>
+        <v>-1.3558</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3527</v>
+        <v>-0.769</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8335</v>
+        <v>-0.5868</v>
       </c>
       <c r="V24" t="n">
         <v>-2.9536</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.4893</v>
+        <v>-12.5237</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.1202</v>
+        <v>-10.5365</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3691</v>
+        <v>-1.9872</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1146</v>
@@ -2404,13 +2404,13 @@
         <v>1.8198</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.645</v>
+        <v>-0.6794</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7181</v>
+        <v>-0.1344</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9268</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-3.2703</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.7603</v>
+        <v>-14.4256</v>
       </c>
       <c r="E26" t="n">
-        <v>-17.9814</v>
+        <v>-17.9815</v>
       </c>
       <c r="F26" t="n">
-        <v>1.221100000000001</v>
+        <v>3.555800000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-2.975499999999999</v>
@@ -2464,13 +2464,13 @@
         <v>1.5053</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2147000000000001</v>
+        <v>-0.2147</v>
       </c>
       <c r="N26" t="n">
         <v>-0.5724</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3576</v>
+        <v>0.3576000000000001</v>
       </c>
       <c r="P26" t="n">
         <v>-3.4122</v>
@@ -2482,13 +2482,13 @@
         <v>11.3736</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.1305</v>
+        <v>-1.7955</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.9316</v>
+        <v>-2.9314</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1986</v>
+        <v>1.136</v>
       </c>
       <c r="V26" t="n">
         <v>-6.2422</v>
